--- a/002_A3/L2_analisis_caso/proyectos.xlsx
+++ b/002_A3/L2_analisis_caso/proyectos.xlsx
@@ -425,28 +425,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>ID_Proyecto</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Proyecto</t>
+          <t>Nombre_Proyecto</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Presupuesto</t>
+          <t>Presupuesto_USD</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Estado</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Responsable</t>
         </is>
       </c>
     </row>
@@ -467,6 +472,11 @@
           <t>Activo</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Juan García</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -485,6 +495,11 @@
           <t>Completado</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>María López</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -503,6 +518,11 @@
           <t>Activo</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Carlos Pérez</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -519,6 +539,11 @@
       <c r="D5" t="inlineStr">
         <is>
           <t>En Pausa</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Laura Gómez</t>
         </is>
       </c>
     </row>
